--- a/data/qa/prospect_to_cash/customer.xlsx
+++ b/data/qa/prospect_to_cash/customer.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +426,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sub_intent</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>canonical_question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>site_scope</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>security_scope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>last_reviewed_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -542,7 +554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0012</t>
+          <t>KB-0018</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,50 +564,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Customer</t>
+          <t>Customer Module</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Customers</t>
-        </is>
-      </c>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>HELP_GENERIC</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>What is a Customer?</t>
+          <t>What is a customer record and what forms does it use?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>A Customer is an organization or person with an approved account who can place Customer Orders — created once a Quotation is accepted.</t>
+          <t>The Customers record is the trading account used for billing, shipping, orders, and receivables. A customer may be created directly or through Move Prospect To Customer. A customer can have one bill-to address and multiple ship-to locations.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>customer,client</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>client,account</t>
-        </is>
-      </c>
+          <t>customer, Customers form, bill to, ship to, customer master</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -603,18 +603,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>customer.md</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Customer Module &gt; Meaning and forms</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -627,10 +625,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="b">
@@ -638,10 +640,696 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0019</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>How are ship-to locations managed for a customer?</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>The Customer Ship Tos form maintains delivery locations; a specific ship-to can carry its own contact and codes.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>customer, ship to, Customer Ship Tos form, delivery locations</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>customer.md</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Customer Module &gt; Meaning and forms</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0020</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>How do I set up and validate a new customer?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Search existing Customers, Prospects, and corporate/subordinate relationships before adding a new account. Enter or allow generation of the customer number; confirm legal name, bill-to address, contact, and site. Set billing terms, currency, language, bank, tax, and credit details as required by the site's accounting policy. Save the customer; add ship-to records through Customer Ship Tos and review each address and shipping contact. Connect sales contacts and salesperson/territory data where CRM uses them. Validate the first estimate or order defaults for customer, ship-to, terms, currency, and tax before processing.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>create customer, customer number, billing terms, Customer Ship Tos, currency</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>customer.md</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Customer Module &gt; Set up and validate a customer</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0021</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>What should I review before entering a customer order?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Review account, bill-to, ship-to, financial codes, and sales links before order entry.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>order entry, bill-to, ship-to, financial codes, sales links</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>customer.md</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Customer Module &gt; Set up and validate a customer</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0022</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>What is the difference between a customer's credit and balance?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Customers can carry a credit limit and a customer-level Credit Hold, while a balance is a live receivable figure that must come from an authorized SyteLine read. Credit configuration and current balance need permission-aware, current ERP data.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>customer balance, credit limit, customer credit hold, corporate credit</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>customer.md</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Customer Module &gt; Credit and balance are separate facts</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HELP_GENERIC</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>How does a customer-level Credit Hold work?</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>A customer-level Credit Hold can prevent shipments without setting each order's Credit Hold checkbox.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>customer credit hold, credit limit, customer balance</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>customer.md</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Customer Module &gt; Credit and balance are separate facts</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>What should I check if an order shows the wrong address for a customer?</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>If an order shows the wrong address, verify the selected customer and ship-to rather than assuming the customer master is wrong.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>wrong ship-to, customer, address, troubleshooting</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>customer.md</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Customer Module &gt; Troubleshooting customer selection</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Customer Module</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>What should I do if I can't select a customer in the system?</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>If the customer cannot be selected, check site, account status, and permissions in the actual application. Do not infer security settings from a missing result alone.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>customer not found, permissions, site, troubleshooting</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>customer.md</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Customer Module &gt; Troubleshooting customer selection</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -658,39 +1346,759 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variation_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_variation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KB-0018</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>What does a customer record do?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0018</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>How are customers set up in the system?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0018</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>What forms are used for customer accounts?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0019</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>How do I manage ship-to addresses for a customer?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0019</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Where do I set up different delivery locations?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0019</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Can a customer have multiple ship-to addresses?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0020</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>What are the steps to create and validate a customer?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0020</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>How do I add a new customer and make sure everything is correct?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0020</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>What's the process for setting up a customer account?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0021</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>What needs to be checked before processing a customer order?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KB-0021</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>What do I need to review before entering an order for a customer?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-0021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Which details should I confirm before starting a customer order?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KB-0022</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>How are credit and balance different for customers?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KB-0022</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>What's the distinction between credit limit and balance?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KB-0022</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Can you explain the difference between customer credit and balance?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KB-0023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>What happens when a customer is on credit hold?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KB-0023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>How does credit hold at the customer level affect shipments?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KB-0023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Does a customer-level credit hold stop all shipments?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KB-0024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Why is the wrong address showing on my order?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KB-0024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>How do I fix an incorrect address on a customer order?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KB-0024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>What do I do if the shipping address is wrong on an order?</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KB-0025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Why can't I find a customer to select?</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KB-0025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Customer isn't showing up when I try to select them—what now?</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KB-0025</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>How do I troubleshoot when a customer can't be selected?</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
